--- a/source/Yard Sale Listing FINAL.xlsx
+++ b/source/Yard Sale Listing FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\13145\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EB9C4B-6928-420A-9059-6BD6F72910BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9D606A-4435-4FB2-BFE5-4E343056B170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="136">
   <si>
     <t>Homeowner Address</t>
   </si>
@@ -77,15 +77,6 @@
   </si>
   <si>
     <t>Kids, baby, clothing, home goods</t>
-  </si>
-  <si>
-    <t>5427 Bischoff Ave</t>
-  </si>
-  <si>
-    <t>Household items, furniture, decor, clothing, appliances, toys, books, &amp; more</t>
-  </si>
-  <si>
-    <t>Cash, Apple Pay, Venmo, Cash App, Zelle</t>
   </si>
   <si>
     <t>5431 Bischoff Ave</t>
@@ -523,6 +514,12 @@
   </si>
   <si>
     <t>Art, tools, office and kitchen furniture, home décor, kitchen items</t>
+  </si>
+  <si>
+    <t>5606 Botanical Ave</t>
+  </si>
+  <si>
+    <t>Household items, toys, bikes</t>
   </si>
 </sst>
 </file>
@@ -958,10 +955,10 @@
     </row>
     <row r="2" spans="1:3" s="8" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>10</v>
@@ -969,7 +966,7 @@
     </row>
     <row r="3" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
@@ -1052,18 +1049,18 @@
         <v>23</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1074,26 +1071,26 @@
         <v>28</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>7</v>
@@ -1101,76 +1098,76 @@
     </row>
     <row r="15" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>7</v>
@@ -1178,43 +1175,43 @@
     </row>
     <row r="22" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="139.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>10</v>
@@ -1222,10 +1219,10 @@
     </row>
     <row r="26" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>10</v>
@@ -1233,43 +1230,43 @@
     </row>
     <row r="27" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>10</v>
@@ -1277,10 +1274,10 @@
     </row>
     <row r="31" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>7</v>
@@ -1288,21 +1285,21 @@
     </row>
     <row r="32" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>10</v>
@@ -1310,10 +1307,10 @@
     </row>
     <row r="34" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>7</v>
@@ -1321,10 +1318,10 @@
     </row>
     <row r="35" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>7</v>
@@ -1332,10 +1329,10 @@
     </row>
     <row r="36" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>10</v>
@@ -1343,10 +1340,10 @@
     </row>
     <row r="37" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>10</v>
@@ -1354,10 +1351,10 @@
     </row>
     <row r="38" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>7</v>
@@ -1365,21 +1362,21 @@
     </row>
     <row r="39" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>10</v>
@@ -1387,10 +1384,10 @@
     </row>
     <row r="41" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>10</v>
@@ -1398,10 +1395,10 @@
     </row>
     <row r="42" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>7</v>
@@ -1409,29 +1406,29 @@
     </row>
     <row r="43" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>12</v>
@@ -1442,10 +1439,10 @@
     </row>
     <row r="46" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>10</v>
@@ -1453,10 +1450,10 @@
     </row>
     <row r="47" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>10</v>
@@ -1464,21 +1461,21 @@
     </row>
     <row r="48" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>7</v>
@@ -1486,10 +1483,10 @@
     </row>
     <row r="50" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>10</v>
@@ -1497,21 +1494,21 @@
     </row>
     <row r="51" spans="1:3" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>10</v>
@@ -1519,21 +1516,21 @@
     </row>
     <row r="53" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>7</v>
@@ -1541,10 +1538,10 @@
     </row>
     <row r="55" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>7</v>
@@ -1552,7 +1549,7 @@
     </row>
     <row r="56" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>13</v>
@@ -1563,10 +1560,10 @@
     </row>
     <row r="57" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>7</v>
@@ -1574,21 +1571,21 @@
     </row>
     <row r="58" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>10</v>
@@ -1596,24 +1593,24 @@
     </row>
     <row r="60" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
